--- a/data/trans_orig/P16-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P16-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas en 2007</t>
+          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>258725</t>
+          <t>253717</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>312582</t>
+          <t>307990</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>367467</t>
+          <t>370894</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>418247</t>
+          <t>420607</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>61,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>638373</t>
+          <t>635208</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>710451</t>
+          <t>716449</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>51,87%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>380412</t>
+          <t>385004</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>434269</t>
+          <t>439277</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>55,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>63,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>270104</t>
+          <t>267744</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>320884</t>
+          <t>317457</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>670894</t>
+          <t>664896</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>742972</t>
+          <t>746137</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>54,02%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>366905</t>
+          <t>364683</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>430503</t>
+          <t>425178</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>541685</t>
+          <t>544198</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>604069</t>
+          <t>604257</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>927908</t>
+          <t>924367</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1019211</t>
+          <t>1017449</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>52,71%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>531297</t>
+          <t>536622</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>594895</t>
+          <t>597117</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>364324</t>
+          <t>364136</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>426708</t>
+          <t>424195</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>910982</t>
+          <t>912744</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1002285</t>
+          <t>1005826</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>52,11%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>239071</t>
+          <t>241441</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>292291</t>
+          <t>291642</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>369204</t>
+          <t>371047</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>425884</t>
+          <t>423097</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>622299</t>
+          <t>626671</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>697164</t>
+          <t>700510</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>51,42%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>386218</t>
+          <t>386867</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>439438</t>
+          <t>437068</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>64,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>257957</t>
+          <t>260744</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>314637</t>
+          <t>312794</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>665186</t>
+          <t>661840</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>740051</t>
+          <t>735679</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>54,0%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>354674</t>
+          <t>352695</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>409779</t>
+          <t>412156</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>585489</t>
+          <t>582916</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>651019</t>
+          <t>648937</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>959409</t>
+          <t>959012</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1046016</t>
+          <t>1046890</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>52,85%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>532443</t>
+          <t>530066</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>587548</t>
+          <t>589527</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>387593</t>
+          <t>389675</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>453123</t>
+          <t>455696</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>934818</t>
+          <t>933944</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1021425</t>
+          <t>1021822</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>51,59%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1273254</t>
+          <t>1278406</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1384974</t>
+          <t>1386547</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1917351</t>
+          <t>1921725</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2039467</t>
+          <t>2034112</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3224177</t>
+          <t>3225281</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3385897</t>
+          <t>3389671</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>50,94%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1890551</t>
+          <t>1888978</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2002271</t>
+          <t>1997119</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1339730</t>
+          <t>1345085</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1461846</t>
+          <t>1457472</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3268825</t>
+          <t>3265051</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3430545</t>
+          <t>3429441</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,53%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas en 2012</t>
+          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas en 2012 (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>340612</t>
+          <t>338937</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>394353</t>
+          <t>392947</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>452992</t>
+          <t>453874</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>504819</t>
+          <t>502254</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>807281</t>
+          <t>805389</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>886986</t>
+          <t>881292</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>63,01%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>307226</t>
+          <t>308632</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>360967</t>
+          <t>362642</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>192231</t>
+          <t>194796</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>244058</t>
+          <t>243176</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>511643</t>
+          <t>517337</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>591348</t>
+          <t>593240</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,42%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>476081</t>
+          <t>474743</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>543865</t>
+          <t>538942</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>702843</t>
+          <t>702531</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>762490</t>
+          <t>763497</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1193450</t>
+          <t>1196694</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1284857</t>
+          <t>1283905</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>58,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>62,66%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>474082</t>
+          <t>479005</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>541866</t>
+          <t>543204</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>268660</t>
+          <t>267653</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>328307</t>
+          <t>328619</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>764240</t>
+          <t>765192</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>855647</t>
+          <t>852403</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,6%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>332337</t>
+          <t>331464</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>390934</t>
+          <t>389038</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>498852</t>
+          <t>499654</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>553797</t>
+          <t>553213</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>845721</t>
+          <t>846002</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>927334</t>
+          <t>928736</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>60,59%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>365604</t>
+          <t>367500</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>424201</t>
+          <t>425074</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>56,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>222486</t>
+          <t>223070</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>277431</t>
+          <t>276629</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>605487</t>
+          <t>604085</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>687100</t>
+          <t>686819</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>44,81%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>458686</t>
+          <t>459576</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>520141</t>
+          <t>520177</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>732376</t>
+          <t>729748</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>790027</t>
+          <t>789640</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1202996</t>
+          <t>1208467</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1295036</t>
+          <t>1297952</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>65,0%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>425789</t>
+          <t>425753</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>487244</t>
+          <t>486354</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>260897</t>
+          <t>261284</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>318548</t>
+          <t>321176</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>701819</t>
+          <t>698903</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>793859</t>
+          <t>788388</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,48%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1667748</t>
+          <t>1659947</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1784240</t>
+          <t>1782840</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2440594</t>
+          <t>2442542</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2553846</t>
+          <t>2556228</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4130658</t>
+          <t>4142304</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4301986</t>
+          <t>4302665</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>59,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>61,67%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1637754</t>
+          <t>1639154</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1754246</t>
+          <t>1762047</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1001561</t>
+          <t>999179</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1114813</t>
+          <t>1112865</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2675415</t>
+          <t>2674736</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2846743</t>
+          <t>2835097</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>40,63%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas en 2016</t>
+          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>312436</t>
+          <t>312935</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>363926</t>
+          <t>364983</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>429341</t>
+          <t>430425</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>478379</t>
+          <t>476475</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>754722</t>
+          <t>758747</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>826914</t>
+          <t>831067</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>61,67%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>310874</t>
+          <t>309817</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>362364</t>
+          <t>361865</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>194460</t>
+          <t>196364</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>243498</t>
+          <t>242414</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>520725</t>
+          <t>516572</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>592917</t>
+          <t>588892</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>43,7%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>465433</t>
+          <t>469364</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>532391</t>
+          <t>535467</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>648188</t>
+          <t>648027</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>709344</t>
+          <t>710939</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1132895</t>
+          <t>1139993</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1226720</t>
+          <t>1230340</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>59,57%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>490040</t>
+          <t>486964</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>556998</t>
+          <t>553067</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>333569</t>
+          <t>331974</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>394725</t>
+          <t>394886</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>838624</t>
+          <t>835004</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>932449</t>
+          <t>925351</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>44,8%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>324903</t>
+          <t>322968</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>384520</t>
+          <t>383324</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>450784</t>
+          <t>455640</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>508444</t>
+          <t>508034</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>794008</t>
+          <t>795026</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>872559</t>
+          <t>875671</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>56,69%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>375032</t>
+          <t>376228</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>434649</t>
+          <t>436584</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>276567</t>
+          <t>276977</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>334227</t>
+          <t>329371</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>672004</t>
+          <t>668892</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>750555</t>
+          <t>749537</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>48,53%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>465759</t>
+          <t>468449</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>527515</t>
+          <t>529844</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>647079</t>
+          <t>646037</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>712726</t>
+          <t>710804</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1136024</t>
+          <t>1132149</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1226120</t>
+          <t>1220107</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>57,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>61,58%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>410052</t>
+          <t>407723</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>471808</t>
+          <t>469118</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>331053</t>
+          <t>332975</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>396700</t>
+          <t>397742</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>755226</t>
+          <t>761239</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>845322</t>
+          <t>849197</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>42,86%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1633568</t>
+          <t>1631591</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1750301</t>
+          <t>1748531</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2232652</t>
+          <t>2246478</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2355591</t>
+          <t>2364311</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3910385</t>
+          <t>3906636</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4079246</t>
+          <t>4069645</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>58,65%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1644049</t>
+          <t>1645819</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1760782</t>
+          <t>1762759</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,87%</t>
+          <t>51,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1188951</t>
+          <t>1180231</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1311890</t>
+          <t>1298064</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2859646</t>
+          <t>2869247</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3028507</t>
+          <t>3032256</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>43,7%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas en 2023</t>
+          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas en 2023 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>323015</t>
+          <t>323267</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>381888</t>
+          <t>379813</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>414720</t>
+          <t>416201</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>455743</t>
+          <t>457304</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>751465</t>
+          <t>751674</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>822403</t>
+          <t>826004</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>63,0%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>253553</t>
+          <t>255628</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>312426</t>
+          <t>312174</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>220009</t>
+          <t>218448</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>261032</t>
+          <t>259551</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>488791</t>
+          <t>485190</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>559729</t>
+          <t>559520</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>42,67%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>235913</t>
+          <t>205005</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>576078</t>
+          <t>573058</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>582375</t>
+          <t>582867</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>633618</t>
+          <t>635321</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>713035</t>
+          <t>709965</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1206982</t>
+          <t>1208478</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>56,18%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>616786</t>
+          <t>619806</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>956951</t>
+          <t>987859</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>51,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>324488</t>
+          <t>322785</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>375731</t>
+          <t>375239</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>943989</t>
+          <t>942493</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1437936</t>
+          <t>1441006</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>66,99%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>347733</t>
+          <t>349892</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>410570</t>
+          <t>411515</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>58,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>520928</t>
+          <t>516958</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>771556</t>
+          <t>781719</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>902956</t>
+          <t>891445</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1240778</t>
+          <t>1213294</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>74,07%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>294110</t>
+          <t>293165</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>356947</t>
+          <t>354788</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>161810</t>
+          <t>151647</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>412438</t>
+          <t>416408</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>397268</t>
+          <t>424752</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>735090</t>
+          <t>746601</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>45,58%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>491316</t>
+          <t>491152</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>559901</t>
+          <t>556129</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>712926</t>
+          <t>713339</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>821802</t>
+          <t>817322</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1224552</t>
+          <t>1223917</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1378389</t>
+          <t>1358646</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>67,32%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>366930</t>
+          <t>370702</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>435515</t>
+          <t>435679</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>269572</t>
+          <t>274052</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>378448</t>
+          <t>378035</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>639816</t>
+          <t>659559</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>793653</t>
+          <t>794288</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>39,36%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1310152</t>
+          <t>1322592</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1859567</t>
+          <t>1860030</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2317771</t>
+          <t>2308673</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2679727</t>
+          <t>2627814</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3634249</t>
+          <t>3690438</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4375000</t>
+          <t>4383430</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>51,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,58%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1600250</t>
+          <t>1599787</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2149665</t>
+          <t>2137225</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>61,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>978871</t>
+          <t>1030784</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1340827</t>
+          <t>1349925</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2743415</t>
+          <t>2734985</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3484166</t>
+          <t>3427977</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>48,16%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P16-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>253717</t>
+          <t>257196</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>307990</t>
+          <t>309976</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>370894</t>
+          <t>368678</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>420607</t>
+          <t>419715</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>635208</t>
+          <t>639776</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>716449</t>
+          <t>712748</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,87%</t>
+          <t>51,6%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>385004</t>
+          <t>383018</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>439277</t>
+          <t>435798</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,39%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>267744</t>
+          <t>268636</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>317457</t>
+          <t>319673</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>664896</t>
+          <t>668597</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>746137</t>
+          <t>741569</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>53,68%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>364683</t>
+          <t>364187</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>425178</t>
+          <t>427178</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>544198</t>
+          <t>542806</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>604257</t>
+          <t>604500</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>924367</t>
+          <t>927815</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1017449</t>
+          <t>1014905</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>52,58%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>536622</t>
+          <t>534622</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>597117</t>
+          <t>597613</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>62,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>364136</t>
+          <t>363893</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>424195</t>
+          <t>425587</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>912744</t>
+          <t>915288</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1005826</t>
+          <t>1002378</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>51,93%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>241441</t>
+          <t>238446</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>291642</t>
+          <t>290352</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>371047</t>
+          <t>367427</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>423097</t>
+          <t>419852</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>626671</t>
+          <t>621955</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>700510</t>
+          <t>696660</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,14%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>386867</t>
+          <t>388157</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>437068</t>
+          <t>440063</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>260744</t>
+          <t>263989</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>312794</t>
+          <t>316414</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>661840</t>
+          <t>665690</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>735679</t>
+          <t>740395</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>48,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>54,35%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>352695</t>
+          <t>354560</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>412156</t>
+          <t>412925</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>582916</t>
+          <t>584415</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>648937</t>
+          <t>647611</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>959012</t>
+          <t>953419</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1046890</t>
+          <t>1042698</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>52,64%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>530066</t>
+          <t>529297</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>589527</t>
+          <t>587662</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>389675</t>
+          <t>391001</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>455696</t>
+          <t>454197</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>43,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>933944</t>
+          <t>938136</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1021822</t>
+          <t>1027415</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>51,87%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1278406</t>
+          <t>1269227</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1386547</t>
+          <t>1384329</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1921725</t>
+          <t>1919943</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2034112</t>
+          <t>2033055</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3225281</t>
+          <t>3227741</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3389671</t>
+          <t>3384674</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>50,86%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1888978</t>
+          <t>1891196</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1997119</t>
+          <t>2006298</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1345085</t>
+          <t>1346142</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1457472</t>
+          <t>1459254</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3265051</t>
+          <t>3270048</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3429441</t>
+          <t>3426981</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>51,5%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>338937</t>
+          <t>338291</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>392947</t>
+          <t>391622</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>55,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>453874</t>
+          <t>450988</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>502254</t>
+          <t>502338</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>805389</t>
+          <t>807604</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>881292</t>
+          <t>885064</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>63,28%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>308632</t>
+          <t>309957</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>362642</t>
+          <t>363288</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>194796</t>
+          <t>194712</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>243176</t>
+          <t>246062</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>517337</t>
+          <t>513565</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>593240</t>
+          <t>591025</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,26%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>474743</t>
+          <t>480839</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>538942</t>
+          <t>545184</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>702531</t>
+          <t>698982</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>763497</t>
+          <t>759453</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1196694</t>
+          <t>1192593</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1283905</t>
+          <t>1284972</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>62,71%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>479005</t>
+          <t>472763</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>543204</t>
+          <t>537108</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>267653</t>
+          <t>271697</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>328619</t>
+          <t>332168</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>765192</t>
+          <t>764125</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>852403</t>
+          <t>856504</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>41,8%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>331464</t>
+          <t>332942</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>389038</t>
+          <t>390667</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>499654</t>
+          <t>495609</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>553213</t>
+          <t>552909</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,26%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>846002</t>
+          <t>847799</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>928736</t>
+          <t>926477</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,44%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>367500</t>
+          <t>365871</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>425074</t>
+          <t>423596</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>223070</t>
+          <t>223374</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>276629</t>
+          <t>280674</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>604085</t>
+          <t>606344</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>686819</t>
+          <t>685022</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>44,69%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>459576</t>
+          <t>458173</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>520177</t>
+          <t>522145</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>729748</t>
+          <t>727505</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>789640</t>
+          <t>788645</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>69,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1208467</t>
+          <t>1208545</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1297952</t>
+          <t>1294219</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>64,81%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>425753</t>
+          <t>423785</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>486354</t>
+          <t>487757</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>261284</t>
+          <t>262279</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>321176</t>
+          <t>323419</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>698903</t>
+          <t>702636</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>788388</t>
+          <t>788310</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1659947</t>
+          <t>1663558</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1782840</t>
+          <t>1785559</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2442542</t>
+          <t>2442617</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2556228</t>
+          <t>2556595</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4142304</t>
+          <t>4138554</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4302665</t>
+          <t>4304306</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>61,69%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1639154</t>
+          <t>1636435</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1762047</t>
+          <t>1758436</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>999179</t>
+          <t>998812</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1112865</t>
+          <t>1112790</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2674736</t>
+          <t>2673095</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2835097</t>
+          <t>2838847</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,69%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>312935</t>
+          <t>313585</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>364983</t>
+          <t>363055</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>430425</t>
+          <t>429892</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>476475</t>
+          <t>478913</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>758747</t>
+          <t>758331</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>831067</t>
+          <t>832459</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>61,77%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>309817</t>
+          <t>311745</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>361865</t>
+          <t>361215</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>196364</t>
+          <t>193926</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>242414</t>
+          <t>242947</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>516572</t>
+          <t>515180</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>588892</t>
+          <t>589308</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,73%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>469364</t>
+          <t>468900</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>535467</t>
+          <t>533207</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>648027</t>
+          <t>650470</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>710939</t>
+          <t>712680</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1139993</t>
+          <t>1137448</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1230340</t>
+          <t>1225797</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>59,35%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>486964</t>
+          <t>489224</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>553067</t>
+          <t>553531</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>331974</t>
+          <t>330233</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>394886</t>
+          <t>392443</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>835004</t>
+          <t>839547</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>925351</t>
+          <t>927896</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>44,93%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>322968</t>
+          <t>325792</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>383324</t>
+          <t>383796</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>455640</t>
+          <t>452165</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>508034</t>
+          <t>508958</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>57,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>795026</t>
+          <t>790620</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>875671</t>
+          <t>873269</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>56,54%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>376228</t>
+          <t>375756</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>436584</t>
+          <t>433760</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>57,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>276977</t>
+          <t>276053</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>329371</t>
+          <t>332846</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>668892</t>
+          <t>671294</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>749537</t>
+          <t>753943</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>48,81%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>468449</t>
+          <t>469422</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>529844</t>
+          <t>527900</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>646037</t>
+          <t>649297</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>710804</t>
+          <t>711944</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>68,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1132149</t>
+          <t>1131990</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1220107</t>
+          <t>1227054</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>61,93%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>407723</t>
+          <t>409667</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>469118</t>
+          <t>468145</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>332975</t>
+          <t>331835</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>397742</t>
+          <t>394482</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>761239</t>
+          <t>754292</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>849197</t>
+          <t>849356</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>42,87%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1631591</t>
+          <t>1631125</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1748531</t>
+          <t>1744987</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>48,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2246478</t>
+          <t>2242521</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2364311</t>
+          <t>2360411</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3906636</t>
+          <t>3904331</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4069645</t>
+          <t>4081280</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>58,82%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1645819</t>
+          <t>1649363</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1762759</t>
+          <t>1763225</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1180231</t>
+          <t>1184131</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1298064</t>
+          <t>1302021</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2869247</t>
+          <t>2857612</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3032256</t>
+          <t>3034561</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,73%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>351154</t>
+          <t>380360</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>323267</t>
+          <t>350757</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>379813</t>
+          <t>408681</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>59,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>436992</t>
+          <t>466792</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>416201</t>
+          <t>443571</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>457304</t>
+          <t>487737</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>788146</t>
+          <t>847153</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>751674</t>
+          <t>809646</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>826004</t>
+          <t>884439</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,33%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>62,12%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>284287</t>
+          <t>310350</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>255628</t>
+          <t>282029</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>312174</t>
+          <t>339953</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>238760</t>
+          <t>266321</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>218448</t>
+          <t>245376</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>259551</t>
+          <t>289542</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>523048</t>
+          <t>576670</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>485190</t>
+          <t>539384</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>559520</t>
+          <t>614177</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>43,14%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1311194</t>
+          <t>1423823</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1311194</t>
+          <t>1423823</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1311194</t>
+          <t>1423823</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>447481</t>
+          <t>489565</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>205005</t>
+          <t>452740</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>573058</t>
+          <t>527495</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>608031</t>
+          <t>675627</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>582867</t>
+          <t>643533</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>635321</t>
+          <t>702575</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>65,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1055512</t>
+          <t>1165191</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>709965</t>
+          <t>1120476</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1208478</t>
+          <t>1210469</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>57,1%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>745383</t>
+          <t>559352</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>619806</t>
+          <t>521422</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>987859</t>
+          <t>596177</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>56,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>350075</t>
+          <t>395211</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>322785</t>
+          <t>368263</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>375239</t>
+          <t>427305</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1095459</t>
+          <t>954564</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>942493</t>
+          <t>909286</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1441006</t>
+          <t>999279</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>47,14%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>381360</t>
+          <t>426926</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>349892</t>
+          <t>396080</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>411515</t>
+          <t>459796</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>627152</t>
+          <t>490464</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>516958</t>
+          <t>461528</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>781719</t>
+          <t>516651</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1008512</t>
+          <t>917390</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>891445</t>
+          <t>874704</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1213294</t>
+          <t>960079</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>54,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>59,44%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>323320</t>
+          <t>376147</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>293165</t>
+          <t>343277</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>354788</t>
+          <t>406993</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>306214</t>
+          <t>321795</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>151647</t>
+          <t>295608</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>416408</t>
+          <t>350731</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>629534</t>
+          <t>697942</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>424752</t>
+          <t>655253</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>746601</t>
+          <t>740628</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,85%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>525632</t>
+          <t>548448</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>491152</t>
+          <t>513333</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>556129</t>
+          <t>581059</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>58,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>750777</t>
+          <t>731693</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>713339</t>
+          <t>701352</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>817322</t>
+          <t>761251</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1276409</t>
+          <t>1280141</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1223917</t>
+          <t>1230893</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1358646</t>
+          <t>1322899</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>60,75%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>62,78%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>401199</t>
+          <t>441614</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>370702</t>
+          <t>409003</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>435679</t>
+          <t>476729</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>340597</t>
+          <t>385338</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>274052</t>
+          <t>355780</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>378035</t>
+          <t>415679</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>741796</t>
+          <t>826952</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>659559</t>
+          <t>784194</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>794288</t>
+          <t>876200</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>41,58%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1091374</t>
+          <t>1117031</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1091374</t>
+          <t>1117031</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1091374</t>
+          <t>1117031</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2018205</t>
+          <t>2107093</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2018205</t>
+          <t>2107093</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2018205</t>
+          <t>2107093</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1705627</t>
+          <t>1845298</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1322592</t>
+          <t>1778416</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1860030</t>
+          <t>1909063</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>52,23%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2422952</t>
+          <t>2364576</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2308673</t>
+          <t>2312258</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2627814</t>
+          <t>2418038</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>4128578</t>
+          <t>4209874</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3690438</t>
+          <t>4126631</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4383430</t>
+          <t>4298084</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>59,15%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1754190</t>
+          <t>1687464</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1599787</t>
+          <t>1623699</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2137225</t>
+          <t>1754346</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1235646</t>
+          <t>1368665</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1030784</t>
+          <t>1315203</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1349925</t>
+          <t>1420983</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2989837</t>
+          <t>3056129</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2734985</t>
+          <t>2967919</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3427977</t>
+          <t>3139372</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>43,21%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3658598</t>
+          <t>3733241</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3658598</t>
+          <t>3733241</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3658598</t>
+          <t>3733241</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7118415</t>
+          <t>7266003</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7118415</t>
+          <t>7266003</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7118415</t>
+          <t>7266003</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
